--- a/results/cpp_dijkstra.xlsx
+++ b/results/cpp_dijkstra.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005371096</v>
+        <v>0.0004655427</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004638672</v>
+        <v>0.0004212372</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0060913079999999</v>
+        <v>0.0055803569999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005786131</v>
+        <v>0.005774638</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04385985</v>
+        <v>0.04278691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04470215</v>
+        <v>0.04197098</v>
       </c>
       <c r="H2" t="n">
-        <v>5.434435000000001</v>
+        <v>5.072400999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>5.407458</v>
+        <v>5.010930999999999</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0004882811</v>
+        <v>0.0003888662</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000354004</v>
+        <v>0.000321689</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004052734</v>
+        <v>0.003392729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0032592789999999</v>
+        <v>0.003337379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02420655</v>
+        <v>0.0249332099999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0229858299999999</v>
+        <v>0.0213649299999999</v>
       </c>
       <c r="H3" t="n">
-        <v>2.784534</v>
+        <v>2.557563</v>
       </c>
       <c r="I3" t="n">
-        <v>2.77345</v>
+        <v>2.511689</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0004516602</v>
+        <v>0.0004226374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000378418</v>
+        <v>0.0003248420999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002917483</v>
+        <v>0.002954014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002917483</v>
+        <v>0.002197549</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0153564399999999</v>
+        <v>0.0182352499999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01735842</v>
+        <v>0.01562887</v>
       </c>
       <c r="H4" t="n">
-        <v>1.827965</v>
+        <v>1.736565</v>
       </c>
       <c r="I4" t="n">
-        <v>1.850722</v>
+        <v>1.726034</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0005126952</v>
+        <v>0.0004400792999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004760742</v>
+        <v>0.0003764933</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003234866</v>
+        <v>0.002388736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002233891</v>
+        <v>0.0017877919999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01342776</v>
+        <v>0.0133361199999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01296386</v>
+        <v>0.0137974999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.404857</v>
+        <v>1.27407</v>
       </c>
       <c r="I5" t="n">
-        <v>1.396033</v>
+        <v>1.300389</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006713869</v>
+        <v>0.000566586</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005981447</v>
+        <v>0.0004843412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002880862</v>
+        <v>0.002898577</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002844241</v>
+        <v>0.002654849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0154662999999999</v>
+        <v>0.01473234</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01419678</v>
+        <v>0.01477877</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466442</v>
+        <v>1.334921</v>
       </c>
       <c r="I6" t="n">
-        <v>1.443394</v>
+        <v>1.304019</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0006591799</v>
+        <v>0.0006080116</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000720215</v>
+        <v>0.0005174731999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00305176</v>
+        <v>0.002432447</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002868655</v>
+        <v>0.002470542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01473388</v>
+        <v>0.01462304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01518556</v>
+        <v>0.0136706499999999</v>
       </c>
       <c r="H7" t="n">
-        <v>1.487572</v>
+        <v>1.423306</v>
       </c>
       <c r="I7" t="n">
-        <v>1.466652</v>
+        <v>1.363111</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000756836</v>
+        <v>0.0007163925</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000720215</v>
+        <v>0.0005718502</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003076174</v>
+        <v>0.002714676</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0027709989999999</v>
+        <v>0.002466275</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0140991299999999</v>
+        <v>0.01555031</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01402587</v>
+        <v>0.0137744899999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.405041</v>
+        <v>1.350807</v>
       </c>
       <c r="I8" t="n">
-        <v>1.431665</v>
+        <v>1.306469</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00078125</v>
+        <v>0.000789714</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007324217999999</v>
+        <v>0.000655857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002917483</v>
+        <v>0.002760025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00292969</v>
+        <v>0.002740961</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0138671899999999</v>
+        <v>0.014103</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01340333</v>
+        <v>0.0130971999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.40979</v>
+        <v>1.309447</v>
       </c>
       <c r="I9" t="n">
-        <v>1.375611</v>
+        <v>1.360028</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0008544916</v>
+        <v>0.0007056972</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000720215</v>
+        <v>0.0007561024999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003015139</v>
+        <v>0.002880862</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00268555</v>
+        <v>0.003008159</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01470947</v>
+        <v>0.01475262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01612549</v>
+        <v>0.01379085</v>
       </c>
       <c r="H10" t="n">
-        <v>1.381909</v>
+        <v>1.297627</v>
       </c>
       <c r="I10" t="n">
-        <v>1.377282</v>
+        <v>1.297795</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0010620097999999</v>
+        <v>0.0011047950999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0009155267999999</v>
+        <v>0.000835326</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003283693</v>
+        <v>0.0028680359999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002966311</v>
+        <v>0.002984608</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01501464</v>
+        <v>0.01421313</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01539306</v>
+        <v>0.0138143599999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.395141</v>
+        <v>1.315902</v>
       </c>
       <c r="I11" t="n">
-        <v>1.381959</v>
+        <v>1.293543</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0011230443999999</v>
+        <v>0.0008846453</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0009643548</v>
+        <v>0.0008619844</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003454591</v>
+        <v>0.003467</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00292969</v>
+        <v>0.0033416589999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01517335</v>
+        <v>0.0154807499999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01674804</v>
+        <v>0.0150478899999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.410205</v>
+        <v>1.297394</v>
       </c>
       <c r="I12" t="n">
-        <v>1.386074</v>
+        <v>1.274859</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0010253894</v>
+        <v>0.001046382</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0011108371999999</v>
+        <v>0.0008911962</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0033447279999999</v>
+        <v>0.0030195319999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003149416</v>
+        <v>0.003089759</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01619872</v>
+        <v>0.01509723</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0158569299999999</v>
+        <v>0.01389303</v>
       </c>
       <c r="H13" t="n">
-        <v>1.403809</v>
+        <v>1.289191</v>
       </c>
       <c r="I13" t="n">
-        <v>1.373815</v>
+        <v>1.32364</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.100000798720245</v>
+        <v>1.197179646881112</v>
       </c>
       <c r="C3" t="n">
-        <v>1.310344515881176</v>
+        <v>1.309454783968367</v>
       </c>
       <c r="D3" t="n">
-        <v>1.503012040760608</v>
+        <v>1.644798921458183</v>
       </c>
       <c r="E3" t="n">
-        <v>1.775279440637079</v>
+        <v>1.730291345394095</v>
       </c>
       <c r="F3" t="n">
-        <v>1.811900084894378</v>
+        <v>1.716061028644132</v>
       </c>
       <c r="G3" t="n">
-        <v>1.944769886490947</v>
+        <v>1.964480108289622</v>
       </c>
       <c r="H3" t="n">
-        <v>1.951649719486277</v>
+        <v>1.983294644159303</v>
       </c>
       <c r="I3" t="n">
-        <v>1.949722547729362</v>
+        <v>1.995044370541098</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.189189572160664</v>
+        <v>1.101517991545471</v>
       </c>
       <c r="C4" t="n">
-        <v>1.225806383417279</v>
+        <v>1.29674447985692</v>
       </c>
       <c r="D4" t="n">
-        <v>2.087864093809596</v>
+        <v>1.8890760165659</v>
       </c>
       <c r="E4" t="n">
-        <v>1.98326125636379</v>
+        <v>2.627763021438885</v>
       </c>
       <c r="F4" t="n">
-        <v>2.856120949907679</v>
+        <v>2.346384612220849</v>
       </c>
       <c r="G4" t="n">
-        <v>2.575243023270551</v>
+        <v>2.685477580912759</v>
       </c>
       <c r="H4" t="n">
-        <v>2.97294258916336</v>
+        <v>2.920939325622709</v>
       </c>
       <c r="I4" t="n">
-        <v>2.921809974701765</v>
+        <v>2.903147330817353</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1.047619716353888</v>
+        <v>1.057860935517998</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9743590389901405</v>
+        <v>1.118843814750488</v>
       </c>
       <c r="D5" t="n">
-        <v>1.883017101790275</v>
+        <v>2.336112906574816</v>
       </c>
       <c r="E5" t="n">
-        <v>2.590158159014921</v>
+        <v>3.230039064947333</v>
       </c>
       <c r="F5" t="n">
-        <v>3.266356413876923</v>
+        <v>3.20834770532961</v>
       </c>
       <c r="G5" t="n">
-        <v>3.448212955092079</v>
+        <v>3.041926435948563</v>
       </c>
       <c r="H5" t="n">
-        <v>3.86831898193197</v>
+        <v>3.981257701696138</v>
       </c>
       <c r="I5" t="n">
-        <v>3.873445685023205</v>
+        <v>3.853409249078545</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8000001191563314</v>
+        <v>0.8216629073079815</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7755100061908097</v>
+        <v>0.8697116825907025</v>
       </c>
       <c r="D6" t="n">
-        <v>2.114404646942443</v>
+        <v>1.925205713010177</v>
       </c>
       <c r="E6" t="n">
-        <v>2.034332182118182</v>
+        <v>2.175128604301036</v>
       </c>
       <c r="F6" t="n">
-        <v>2.835833392601998</v>
+        <v>2.904284723268673</v>
       </c>
       <c r="G6" t="n">
-        <v>3.148752745340845</v>
+        <v>2.839950821347108</v>
       </c>
       <c r="H6" t="n">
-        <v>3.70586426193467</v>
+        <v>3.799776166529704</v>
       </c>
       <c r="I6" t="n">
-        <v>3.746349229662864</v>
+        <v>3.842682506926663</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8148148934759692</v>
+        <v>0.765680621882872</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6440676742361656</v>
+        <v>0.8140270839148412</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995998374708332</v>
+        <v>2.294133027358828</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0170187770924</v>
+        <v>2.337397218909859</v>
       </c>
       <c r="F7" t="n">
-        <v>2.976802444434188</v>
+        <v>2.925992816815108</v>
       </c>
       <c r="G7" t="n">
-        <v>2.943727462141666</v>
+        <v>3.07015247994794</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65322485230967</v>
+        <v>3.563816213800828</v>
       </c>
       <c r="I7" t="n">
-        <v>3.686940051218695</v>
+        <v>3.676099011745926</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7096776580395224</v>
+        <v>0.6498430678713136</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6440676742361656</v>
+        <v>0.7366215837644194</v>
       </c>
       <c r="D8" t="n">
-        <v>1.980157169262825</v>
+        <v>2.055625422702341</v>
       </c>
       <c r="E8" t="n">
-        <v>2.088102882751025</v>
+        <v>2.341441242359429</v>
       </c>
       <c r="F8" t="n">
-        <v>3.110819603762807</v>
+        <v>2.75151492156748</v>
       </c>
       <c r="G8" t="n">
-        <v>3.187121369298304</v>
+        <v>3.04700791100072</v>
       </c>
       <c r="H8" t="n">
-        <v>3.867812398357059</v>
+        <v>3.755089365098048</v>
       </c>
       <c r="I8" t="n">
-        <v>3.777041416811894</v>
+        <v>3.835476387116723</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.687500288</v>
+        <v>0.5895079737727836</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6333334152534281</v>
+        <v>0.642269885051162</v>
       </c>
       <c r="D9" t="n">
-        <v>2.087864093809596</v>
+        <v>2.021850164400648</v>
       </c>
       <c r="E9" t="n">
-        <v>1.974997696001966</v>
+        <v>2.106793201362588</v>
       </c>
       <c r="F9" t="n">
-        <v>3.162850584725551</v>
+        <v>3.033887116216408</v>
       </c>
       <c r="G9" t="n">
-        <v>3.335152532989937</v>
+        <v>3.204576550713154</v>
       </c>
       <c r="H9" t="n">
-        <v>3.854783336525298</v>
+        <v>3.873697064486</v>
       </c>
       <c r="I9" t="n">
-        <v>3.930949956055891</v>
+        <v>3.68443223227757</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6285721240559884</v>
+        <v>0.6596918621754486</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6440676742361656</v>
+        <v>0.5571165285130729</v>
       </c>
       <c r="D10" t="n">
-        <v>2.020241189543799</v>
+        <v>1.937044190245801</v>
       </c>
       <c r="E10" t="n">
-        <v>2.154542272532628</v>
+        <v>1.919658502093806</v>
       </c>
       <c r="F10" t="n">
-        <v>2.981742374130407</v>
+        <v>2.900292287064941</v>
       </c>
       <c r="G10" t="n">
-        <v>2.772142117851923</v>
+        <v>3.043393264374567</v>
       </c>
       <c r="H10" t="n">
-        <v>3.932556340540514</v>
+        <v>3.908982319264318</v>
       </c>
       <c r="I10" t="n">
-        <v>3.926180695021064</v>
+        <v>3.861111346553192</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5057482520406598</v>
+        <v>0.4213837479909552</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5066669812397088</v>
+        <v>0.5042788085130835</v>
       </c>
       <c r="D11" t="n">
-        <v>1.855017506204113</v>
+        <v>1.945706748450889</v>
       </c>
       <c r="E11" t="n">
-        <v>1.950615090595693</v>
+        <v>1.934806178901886</v>
       </c>
       <c r="F11" t="n">
-        <v>2.921138968366874</v>
+        <v>3.010379135348794</v>
       </c>
       <c r="G11" t="n">
-        <v>2.904045719304674</v>
+        <v>3.038213858622499</v>
       </c>
       <c r="H11" t="n">
-        <v>3.895258615437437</v>
+        <v>3.854695106474494</v>
       </c>
       <c r="I11" t="n">
-        <v>3.912893218973934</v>
+        <v>3.873803190152936</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4782621239196311</v>
+        <v>0.526247864539607</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4810130047571703</v>
+        <v>0.4886830898563825</v>
       </c>
       <c r="D12" t="n">
-        <v>1.763250121360213</v>
+        <v>1.60956359965385</v>
       </c>
       <c r="E12" t="n">
-        <v>1.974997696001966</v>
+        <v>1.728075186606465</v>
       </c>
       <c r="F12" t="n">
-        <v>2.890584478707734</v>
+        <v>2.76387836506631</v>
       </c>
       <c r="G12" t="n">
-        <v>2.669097398859807</v>
+        <v>2.78916047366111</v>
       </c>
       <c r="H12" t="n">
-        <v>3.853648937565815</v>
+        <v>3.909684336446753</v>
       </c>
       <c r="I12" t="n">
-        <v>3.901276555219996</v>
+        <v>3.930576636318211</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5238103690168828</v>
+        <v>0.4449070224831849</v>
       </c>
       <c r="C13" t="n">
-        <v>0.417583422665393</v>
+        <v>0.4726649417939618</v>
       </c>
       <c r="D13" t="n">
-        <v>1.821166922990474</v>
+        <v>1.848086723373054</v>
       </c>
       <c r="E13" t="n">
-        <v>1.837207596582985</v>
+        <v>1.868960653565537</v>
       </c>
       <c r="F13" t="n">
-        <v>2.707612082930009</v>
+        <v>2.834090094672996</v>
       </c>
       <c r="G13" t="n">
-        <v>2.819092346374757</v>
+        <v>3.021009815713346</v>
       </c>
       <c r="H13" t="n">
-        <v>3.871206837967273</v>
+        <v>3.934561286884565</v>
       </c>
       <c r="I13" t="n">
-        <v>3.936088920269468</v>
+        <v>3.785720437581215</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5500003993601227</v>
+        <v>0.5985898234405562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6551722579405882</v>
+        <v>0.6547273919841835</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7515060203803039</v>
+        <v>0.8223994607290914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8876397203185393</v>
+        <v>0.8651456726970476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9059500424471888</v>
+        <v>0.8580305143220662</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9723849432454733</v>
+        <v>0.982240054144811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9758248597431385</v>
+        <v>0.9916473220796514</v>
       </c>
       <c r="I3" t="n">
-        <v>0.974861273864681</v>
+        <v>0.9975221852705489</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3963965240535547</v>
+        <v>0.3671726638484905</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4086021278057597</v>
+        <v>0.4322481599523067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.695954697936532</v>
+        <v>0.6296920055219666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6610870854545968</v>
+        <v>0.8759210071462951</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9520403166358932</v>
+        <v>0.7821282040736163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8584143410901838</v>
+        <v>0.8951591936375864</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9909808630544532</v>
+        <v>0.9736464418742363</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9739366582339217</v>
+        <v>0.9677157769391177</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2619049290884721</v>
+        <v>0.2644652338794996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2435897597475351</v>
+        <v>0.2797109536876221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4707542754475688</v>
+        <v>0.584028226643704</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6475395397537301</v>
+        <v>0.8075097662368333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8165891034692309</v>
+        <v>0.8020869263324025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8620532387730198</v>
+        <v>0.7604816089871408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9670797454829925</v>
+        <v>0.9953144254240346</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9683614212558013</v>
+        <v>0.9633523122696362</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1600000238312663</v>
+        <v>0.1643325814615963</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1551020012381619</v>
+        <v>0.1739423365181405</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4228809293884886</v>
+        <v>0.3850411426020354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4068664364236364</v>
+        <v>0.4350257208602072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5671666785203996</v>
+        <v>0.5808569446537345</v>
       </c>
       <c r="G6" t="n">
-        <v>0.629750549068169</v>
+        <v>0.5679901642694216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7411728523869339</v>
+        <v>0.7599552333059408</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7492698459325727</v>
+        <v>0.7685365013853326</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1358024822459949</v>
+        <v>0.1276134369804787</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1073446123726943</v>
+        <v>0.1356711806524735</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3326663957847221</v>
+        <v>0.3823555045598047</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3361697961820667</v>
+        <v>0.3895662031516431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4961337407390314</v>
+        <v>0.4876654694691847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4906212436902777</v>
+        <v>0.5116920799913233</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6088708087182784</v>
+        <v>0.5939693689668046</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6144900085364491</v>
+        <v>0.612683168624321</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1013825225770746</v>
+        <v>0.09283472398161623</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09200966774802366</v>
+        <v>0.1052316548234885</v>
       </c>
       <c r="D8" t="n">
-        <v>0.282879595608975</v>
+        <v>0.2936607746717629</v>
       </c>
       <c r="E8" t="n">
-        <v>0.298300411821575</v>
+        <v>0.3344916060513469</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4444028005375439</v>
+        <v>0.3930735602239257</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4553030527569006</v>
+        <v>0.4352868444286742</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5525446283367227</v>
+        <v>0.5364413378711498</v>
       </c>
       <c r="I8" t="n">
-        <v>0.539577345258842</v>
+        <v>0.5479251981595319</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.08593753599999999</v>
+        <v>0.07368849672159795</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07916667690667852</v>
+        <v>0.08028373563139525</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2609830117261995</v>
+        <v>0.252731270550081</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2468747120002457</v>
+        <v>0.2633491501703235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3953563230906939</v>
+        <v>0.379235889527051</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4168940666237421</v>
+        <v>0.4005720688391443</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4818479170656623</v>
+        <v>0.48421213306075</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4913687445069864</v>
+        <v>0.4605540290346963</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06984134711733204</v>
+        <v>0.07329909579727206</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07156307491512952</v>
+        <v>0.06190183650145255</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2244712432826443</v>
+        <v>0.2152271322495335</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2393935858369587</v>
+        <v>0.213295389121534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3313047082367119</v>
+        <v>0.3222546985627713</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3080157908724359</v>
+        <v>0.3381548071527297</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4369507045045015</v>
+        <v>0.4343313688071464</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4362422994467849</v>
+        <v>0.4290123718392436</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05057482520406598</v>
+        <v>0.04213837479909552</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05066669812397088</v>
+        <v>0.05042788085130835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1855017506204112</v>
+        <v>0.1945706748450889</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1950615090595693</v>
+        <v>0.1934806178901886</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2921138968366874</v>
+        <v>0.3010379135348794</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2904045719304674</v>
+        <v>0.3038213858622499</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3895258615437437</v>
+        <v>0.3854695106474494</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3912893218973935</v>
+        <v>0.3873803190152936</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.04347837490178465</v>
+        <v>0.0478407149581461</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04372845497792457</v>
+        <v>0.04442573544148932</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1602954655782012</v>
+        <v>0.1463239636048955</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1795452450910878</v>
+        <v>0.1570977442369514</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2627804071552485</v>
+        <v>0.2512616695514827</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2426452180781643</v>
+        <v>0.2535600430601009</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3503317215968923</v>
+        <v>0.3554258487678866</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3546615050199997</v>
+        <v>0.357325148756201</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04365086408474023</v>
+        <v>0.03707558520693208</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03479861855544942</v>
+        <v>0.03938874514949682</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1517639102492062</v>
+        <v>0.1540072269477545</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1531006330485821</v>
+        <v>0.1557467211304614</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2256343402441674</v>
+        <v>0.236174174556083</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2349243621978964</v>
+        <v>0.2517508179761122</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3226005698306061</v>
+        <v>0.3278801072403804</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3280074100224557</v>
+        <v>0.315476703131768</v>
       </c>
     </row>
   </sheetData>
